--- a/steno/English Sounds.xlsx
+++ b/steno/English Sounds.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DAVIDCORZO\Repositories\self-education-notes\Steno\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DAVIDCORZO\Repositories\self-education-notes\steno\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B68239-472F-4C3F-B2D0-A1F4C47C5DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F05BAE-E2C6-4E4A-A967-6C3770D42AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5565" yWindow="2505" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Long vowels &amp; dipthongs" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="57">
   <si>
     <t>Long vowels</t>
   </si>
@@ -52,54 +52,30 @@
     <t>U</t>
   </si>
   <si>
-    <t>a'</t>
-  </si>
-  <si>
     <t>grape</t>
   </si>
   <si>
-    <t>ee'</t>
-  </si>
-  <si>
     <t>seen</t>
   </si>
   <si>
-    <t>i'</t>
-  </si>
-  <si>
     <t>spite</t>
   </si>
   <si>
-    <t>oh'</t>
-  </si>
-  <si>
     <t>boat</t>
   </si>
   <si>
-    <t>oo', 'ew'</t>
-  </si>
-  <si>
     <t>glue, few</t>
   </si>
   <si>
     <t>Dipthongs</t>
   </si>
   <si>
-    <t>aw'</t>
-  </si>
-  <si>
     <t>bought</t>
   </si>
   <si>
     <t>no 'oo'</t>
   </si>
   <si>
-    <t>ow'</t>
-  </si>
-  <si>
-    <t>oi'</t>
-  </si>
-  <si>
     <t>down</t>
   </si>
   <si>
@@ -227,13 +203,16 @@
   </si>
   <si>
     <t>'ng', 'nj'</t>
+  </si>
+  <si>
+    <t>␣</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,16 +228,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF202122"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -281,22 +280,277 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -578,369 +832,404 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="2.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="3"/>
+      <c r="I1" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="19"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C3" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D3" s="23"/>
+      <c r="E3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B6" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D10" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="E10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" t="s">
-        <v>22</v>
-      </c>
+      <c r="F10" s="15"/>
+      <c r="G10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="16"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1C28F3E-2D49-4C2A-A6D9-C31D49C2DD14}">
-  <dimension ref="B1:C25"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="4"/>
-    </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="4"/>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>